--- a/Piaui/2026/Julho/Dados/gabarito_3serie_lp 3ª SIMULA.xlsx
+++ b/Piaui/2026/Julho/Dados/gabarito_3serie_lp 3ª SIMULA.xlsx
@@ -9,7 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Planilha2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="LP_3EM_S3" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -267,44 +267,48 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -504,454 +508,454 @@
   <dimension ref="A1:AM27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="32.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="32.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-      <c r="AK1" s="2"/>
-      <c r="AL1" s="2"/>
-      <c r="AM1" s="2"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="3"/>
+      <c r="AE1" s="3"/>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>1.31370481608546</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="5" t="n">
         <v>-0.968423168030579</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="5" t="n">
         <v>0.0262740963217091</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="5" t="n">
         <v>201.578841598471</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="5" t="n">
         <v>0.036676474322631</v>
       </c>
-      <c r="H13" s="0" t="s">
+      <c r="H13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>1.08556921188172</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="5" t="n">
         <v>-0.547830583464521</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="5" t="n">
         <v>0.0217113842376344</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="5" t="n">
         <v>222.608470826774</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="5" t="n">
         <v>0.0202347578937095</v>
       </c>
-      <c r="H14" s="0" t="s">
+      <c r="H14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>0.643</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="6" t="n">
         <v>0.857</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="6" t="n">
         <v>0.013</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="6" t="n">
         <v>292.832</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="6" t="n">
         <v>0.087</v>
       </c>
-      <c r="H15" s="0" t="s">
+      <c r="H15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="5" t="n">
         <v>0.593</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="5" t="n">
         <v>2.802</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="5" t="n">
         <v>0.012</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="5" t="n">
         <v>390.111</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="5" t="n">
         <v>0.107</v>
       </c>
-      <c r="H20" s="0" t="s">
+      <c r="H20" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="5" t="n">
         <v>0.784820764204728</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="5" t="n">
         <v>0.993090280215036</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="5" t="n">
         <v>0.0156964152840946</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="5" t="n">
         <v>299.654514010752</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="5" t="n">
         <v>0.178494837460805</v>
       </c>
-      <c r="H24" s="0" t="s">
+      <c r="H24" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="5" t="n">
         <v>0.84445725224476</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="5" t="n">
         <v>1.66650434769531</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="5" t="n">
         <v>0.0168891450448952</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="5" t="n">
         <v>333.325217384766</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="5" t="n">
         <v>0.214157847906194</v>
       </c>
-      <c r="H25" s="0" t="s">
+      <c r="H25" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="6" t="n">
         <v>0.569</v>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D26" s="6" t="n">
         <v>-0.504</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="6" t="n">
         <v>0.011</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="6" t="n">
         <v>224.808</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G26" s="6" t="n">
         <v>0.015</v>
       </c>
-      <c r="H26" s="0" t="s">
+      <c r="H26" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="6" t="n">
         <v>1.029</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D27" s="6" t="n">
         <v>-0.637</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="6" t="n">
         <v>0.021</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="6" t="n">
         <v>218.164</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="6" t="n">
         <v>0.065</v>
       </c>
-      <c r="H27" s="0" t="s">
+      <c r="H27" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -974,347 +978,347 @@
   <dimension ref="A1:G27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="6" width="8.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="32.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="7" width="8.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="7" width="32.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="9" t="n">
         <v>1.31370481608546</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="9" t="n">
         <v>-0.968423168030579</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="9" t="n">
         <v>0.0262740963217091</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="9" t="n">
         <v>201.578841598471</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F13" s="9" t="n">
         <v>0.036676474322631</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="9" t="n">
         <v>1.08556921188172</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C14" s="9" t="n">
         <v>-0.547830583464521</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="9" t="n">
         <v>0.0217113842376344</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="9" t="n">
         <v>222.608470826774</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="9" t="n">
         <v>0.0202347578937095</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="9" t="n">
+      <c r="B15" s="10" t="n">
         <v>0.643</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="10" t="n">
         <v>0.857</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="10" t="n">
         <v>0.013</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="10" t="n">
         <v>292.832</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="10" t="n">
         <v>0.087</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="9" t="n">
         <v>0.593</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="9" t="n">
         <v>2.802</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="9" t="n">
         <v>0.012</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="9" t="n">
         <v>390.111</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="9" t="n">
         <v>0.107</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="8" t="n">
+      <c r="B24" s="9" t="n">
         <v>0.784820764204728</v>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="9" t="n">
         <v>0.993090280215036</v>
       </c>
-      <c r="D24" s="8" t="n">
+      <c r="D24" s="9" t="n">
         <v>0.0156964152840946</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="9" t="n">
         <v>299.654514010752</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="9" t="n">
         <v>0.178494837460805</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B25" s="9" t="n">
         <v>0.84445725224476</v>
       </c>
-      <c r="C25" s="8" t="n">
+      <c r="C25" s="9" t="n">
         <v>1.66650434769531</v>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D25" s="9" t="n">
         <v>0.0168891450448952</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="9" t="n">
         <v>333.325217384766</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F25" s="9" t="n">
         <v>0.214157847906194</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="10" t="n">
         <v>0.569</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C26" s="10" t="n">
         <v>-0.504</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="10" t="n">
         <v>0.011</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="10" t="n">
         <v>224.808</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="10" t="n">
         <v>0.015</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="7" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" s="10" t="n">
         <v>1.029</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C27" s="10" t="n">
         <v>-0.637</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="10" t="n">
         <v>0.021</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="10" t="n">
         <v>218.164</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="10" t="n">
         <v>0.065</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="7" t="s">
         <v>33</v>
       </c>
     </row>
